--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_nuble.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:29</t>
+    <t xml:space="preserve">2026-09-24 01:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -973,7 +973,7 @@
         <v>-0.46</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>-0.08</v>
@@ -996,7 +996,7 @@
         <v>-0.23</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.08</v>
@@ -1019,7 +1019,7 @@
         <v>-0.35</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.12</v>
@@ -1042,10 +1042,10 @@
         <v>-0.2</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="23">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_nuble.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:20</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_nuble.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-05 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
